--- a/Sales Sample Data_Student.xlsx
+++ b/Sales Sample Data_Student.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr filterPrivacy="1" hidePivotFieldList="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25241E35-8548-4615-80E6-12E887A42E77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4158B04-356E-4B0E-9521-CF7332B4707C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -312,7 +312,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -329,7 +329,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -340,168 +339,9 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="78">
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
+  <dxfs count="25">
     <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
@@ -520,6 +360,55 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="d/mm/yyyy"/>
     </dxf>
     <dxf>
       <font>
@@ -589,55 +478,6 @@
           <bgColor rgb="FFDFD8E7"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="d/mm/yyyy"/>
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
@@ -10894,7 +10734,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7B37B118-DC0D-400B-A108-AB5088FBD3D7}" name="PivotTable6" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7B37B118-DC0D-400B-A108-AB5088FBD3D7}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15">
   <location ref="O3:P16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0">
@@ -11022,7 +10862,7 @@
     <dataField name="Average of Call Drop Rate (%)" fld="8" subtotal="average" baseField="9" baseItem="1" numFmtId="10"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="54">
+    <format dxfId="1">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="9" count="12">
@@ -11042,7 +10882,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="47">
+    <format dxfId="0">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -11079,7 +10919,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2FEDFAEA-B637-422D-944E-8FAF12E175D9}" name="PivotTable5" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2FEDFAEA-B637-422D-944E-8FAF12E175D9}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="13">
   <location ref="L3:M16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0">
@@ -11207,7 +11047,7 @@
     <dataField name="Average of Average Duration (sec)" fld="4" subtotal="average" baseField="9" baseItem="3" numFmtId="2"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="55">
+    <format dxfId="3">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="9" count="12">
@@ -11227,7 +11067,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="56">
+    <format dxfId="2">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
   </formats>
@@ -11255,7 +11095,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{86AFCD4A-0B74-49E0-BC25-96D3C93BDBBB}" name="PivotTable4" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{86AFCD4A-0B74-49E0-BC25-96D3C93BDBBB}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9">
   <location ref="I3:J16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0">
@@ -11383,7 +11223,7 @@
     <dataField name="Sum of Deal Value ($)" fld="7" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="57">
+    <format dxfId="4">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="9" count="12">
@@ -11428,7 +11268,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4E619680-0B20-4358-864D-8F528A5032BE}" name="PivotTable3" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4E619680-0B20-4358-864D-8F528A5032BE}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="D3:F16" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0">
@@ -11565,7 +11405,7 @@
     <dataField name="Sum of Deals Closed" fld="5" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="58">
+    <format dxfId="6">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -11574,7 +11414,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="59">
+    <format dxfId="5">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -11617,7 +11457,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{58A4E055-08D3-4608-B591-83EB415E6089}" name="PivotTable1" cacheId="6" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{58A4E055-08D3-4608-B591-83EB415E6089}" name="PivotTable1" cacheId="0" dataOnRows="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0">
@@ -11722,7 +11562,7 @@
     <dataField name="Sum of Deal Value ($)" fld="7" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="4">
-    <format dxfId="74">
+    <format dxfId="10">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -11731,7 +11571,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="73">
+    <format dxfId="9">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -11740,7 +11580,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="72">
+    <format dxfId="8">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -11749,7 +11589,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="71">
+    <format dxfId="7">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -11772,7 +11612,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DDA2B476-C673-45D0-A2D6-CAA31F34258E}" name="PivotTable2" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Name">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{DDA2B476-C673-45D0-A2D6-CAA31F34258E}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Name">
   <location ref="D9:H36" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
@@ -11969,26 +11809,26 @@
     <dataField name=" Deal Value ($)" fld="7" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="11">
-    <format dxfId="70">
+    <format dxfId="24">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="69">
+    <format dxfId="23">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="68">
+    <format dxfId="22">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="67">
+    <format dxfId="21">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="66">
+    <format dxfId="20">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="65">
+    <format dxfId="19">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="4">
@@ -12000,7 +11840,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="64">
+    <format dxfId="18">
       <pivotArea outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -12009,10 +11849,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="63">
+    <format dxfId="17">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="62">
+    <format dxfId="16">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="4">
@@ -12024,10 +11864,10 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="61">
+    <format dxfId="15">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="60">
+    <format dxfId="14">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="4">
@@ -12041,12 +11881,51 @@
     </format>
   </formats>
   <conditionalFormats count="4">
-    <conditionalFormat priority="5">
+    <conditionalFormat priority="1">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="2">
             <reference field="4294967294" count="1" selected="0">
+              <x v="3"/>
+            </reference>
+            <reference field="0" count="26">
               <x v="0"/>
+              <x v="1"/>
+              <x v="2"/>
+              <x v="3"/>
+              <x v="4"/>
+              <x v="5"/>
+              <x v="6"/>
+              <x v="7"/>
+              <x v="8"/>
+              <x v="9"/>
+              <x v="10"/>
+              <x v="11"/>
+              <x v="12"/>
+              <x v="13"/>
+              <x v="14"/>
+              <x v="15"/>
+              <x v="16"/>
+              <x v="17"/>
+              <x v="18"/>
+              <x v="19"/>
+              <x v="20"/>
+              <x v="21"/>
+              <x v="22"/>
+              <x v="23"/>
+              <x v="24"/>
+              <x v="25"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat priority="2">
+      <pivotAreas count="1">
+        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+          <references count="2">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="2"/>
             </reference>
             <reference field="0" count="26">
               <x v="0"/>
@@ -12119,51 +11998,12 @@
         </pivotArea>
       </pivotAreas>
     </conditionalFormat>
-    <conditionalFormat priority="2">
+    <conditionalFormat priority="5">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="2">
             <reference field="4294967294" count="1" selected="0">
-              <x v="2"/>
-            </reference>
-            <reference field="0" count="26">
               <x v="0"/>
-              <x v="1"/>
-              <x v="2"/>
-              <x v="3"/>
-              <x v="4"/>
-              <x v="5"/>
-              <x v="6"/>
-              <x v="7"/>
-              <x v="8"/>
-              <x v="9"/>
-              <x v="10"/>
-              <x v="11"/>
-              <x v="12"/>
-              <x v="13"/>
-              <x v="14"/>
-              <x v="15"/>
-              <x v="16"/>
-              <x v="17"/>
-              <x v="18"/>
-              <x v="19"/>
-              <x v="20"/>
-              <x v="21"/>
-              <x v="22"/>
-              <x v="23"/>
-              <x v="24"/>
-              <x v="25"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat priority="1">
-      <pivotAreas count="1">
-        <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-          <references count="2">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="3"/>
             </reference>
             <reference field="0" count="26">
               <x v="0"/>
@@ -12265,14 +12105,14 @@
   <autoFilter ref="A1:I313" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Name"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Date" dataDxfId="77"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Date" dataDxfId="13"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Total Calls"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Calls Reached"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Average Duration (sec)"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Deals Closed"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Call Conversion Rate (%)" dataDxfId="76"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Call Conversion Rate (%)" dataDxfId="12"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Deal Value ($)"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Call Drop Rate (%)" dataDxfId="75"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Call Drop Rate (%)" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -21746,13 +21586,13 @@
       <c r="L4" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="M4" s="16">
+      <c r="M4" s="15">
         <v>251.7</v>
       </c>
       <c r="O4" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="P4" s="17">
+      <c r="P4" s="16">
         <v>4.1100000000000005E-2</v>
       </c>
     </row>
@@ -21781,13 +21621,13 @@
       <c r="L5" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="M5" s="16">
+      <c r="M5" s="15">
         <v>247.66</v>
       </c>
       <c r="O5" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="P5" s="17">
+      <c r="P5" s="16">
         <v>3.9900000000000005E-2</v>
       </c>
     </row>
@@ -21816,13 +21656,13 @@
       <c r="L6" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="M6" s="16">
+      <c r="M6" s="15">
         <v>252.77</v>
       </c>
       <c r="O6" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="P6" s="17">
+      <c r="P6" s="16">
         <v>4.0800000000000003E-2</v>
       </c>
     </row>
@@ -21851,13 +21691,13 @@
       <c r="L7" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="M7" s="16">
+      <c r="M7" s="15">
         <v>246.21</v>
       </c>
       <c r="O7" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="P7" s="17">
+      <c r="P7" s="16">
         <v>4.3299999999999998E-2</v>
       </c>
     </row>
@@ -21880,13 +21720,13 @@
       <c r="L8" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="M8" s="16">
+      <c r="M8" s="15">
         <v>258.11</v>
       </c>
       <c r="O8" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="P8" s="17">
+      <c r="P8" s="16">
         <v>4.1599999999999998E-2</v>
       </c>
     </row>
@@ -21909,13 +21749,13 @@
       <c r="L9" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="M9" s="16">
+      <c r="M9" s="15">
         <v>219.53</v>
       </c>
       <c r="O9" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="P9" s="17">
+      <c r="P9" s="16">
         <v>4.3499999999999997E-2</v>
       </c>
     </row>
@@ -21938,13 +21778,13 @@
       <c r="L10" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="M10" s="16">
+      <c r="M10" s="15">
         <v>246.06</v>
       </c>
       <c r="O10" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="P10" s="17">
+      <c r="P10" s="16">
         <v>3.7200000000000004E-2</v>
       </c>
     </row>
@@ -21967,13 +21807,13 @@
       <c r="L11" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="M11" s="16">
+      <c r="M11" s="15">
         <v>255.17</v>
       </c>
       <c r="O11" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="P11" s="17">
+      <c r="P11" s="16">
         <v>3.8199999999999998E-2</v>
       </c>
     </row>
@@ -21996,13 +21836,13 @@
       <c r="L12" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="M12" s="16">
+      <c r="M12" s="15">
         <v>262.27999999999997</v>
       </c>
       <c r="O12" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="P12" s="17">
+      <c r="P12" s="16">
         <v>4.4299999999999999E-2</v>
       </c>
     </row>
@@ -22025,13 +21865,13 @@
       <c r="L13" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="M13" s="16">
+      <c r="M13" s="15">
         <v>248.37</v>
       </c>
       <c r="O13" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="P13" s="17">
+      <c r="P13" s="16">
         <v>4.2699999999999995E-2</v>
       </c>
     </row>
@@ -22054,13 +21894,13 @@
       <c r="L14" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="M14" s="16">
+      <c r="M14" s="15">
         <v>237.95</v>
       </c>
       <c r="O14" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="P14" s="17">
+      <c r="P14" s="16">
         <v>4.4299999999999999E-2</v>
       </c>
     </row>
@@ -22083,13 +21923,13 @@
       <c r="L15" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="M15" s="16">
+      <c r="M15" s="15">
         <v>219.19</v>
       </c>
       <c r="O15" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="P15" s="17">
+      <c r="P15" s="16">
         <v>3.8699999999999998E-2</v>
       </c>
     </row>
@@ -22106,19 +21946,19 @@
       <c r="I16" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="J16" s="14">
+      <c r="J16" s="13">
         <v>49072.98</v>
       </c>
       <c r="L16" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="M16" s="16">
+      <c r="M16" s="15">
         <v>245.41666666666663</v>
       </c>
       <c r="O16" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="P16" s="17">
+      <c r="P16" s="16">
         <v>4.130000000000001E-2</v>
       </c>
     </row>
@@ -22157,19 +21997,19 @@
     <row r="7" spans="2:8" s="3" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="2:8" s="3" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="2:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="H9" s="14" t="s">
         <v>47</v>
       </c>
     </row>
@@ -22177,16 +22017,16 @@
       <c r="D10" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="12">
         <v>453</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="4">
         <v>184</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="4">
         <v>92</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="4">
         <v>50524.4</v>
       </c>
     </row>
@@ -22194,16 +22034,16 @@
       <c r="D11" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="12">
         <v>660</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="4">
         <v>92</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="4">
         <v>71</v>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="4">
         <v>49072.98</v>
       </c>
     </row>
@@ -22211,16 +22051,16 @@
       <c r="D12" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="12">
         <v>783</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="4">
         <v>181</v>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="4">
         <v>77</v>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="4">
         <v>49041</v>
       </c>
     </row>
@@ -22228,16 +22068,16 @@
       <c r="D13" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="12">
         <v>379</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="4">
         <v>87</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="4">
         <v>18</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="4">
         <v>45591.429999999993</v>
       </c>
     </row>
@@ -22245,16 +22085,16 @@
       <c r="D14" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="12">
         <v>1023</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="4">
         <v>76</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="4">
         <v>64</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="4">
         <v>45365.2</v>
       </c>
     </row>
@@ -22262,16 +22102,16 @@
       <c r="D15" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="12">
         <v>907</v>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="4">
         <v>141</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="4">
         <v>53</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="4">
         <v>45196.26</v>
       </c>
     </row>
@@ -22279,16 +22119,16 @@
       <c r="D16" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="12">
         <v>288</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="4">
         <v>180</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="4">
         <v>81</v>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="4">
         <v>44979.729999999996</v>
       </c>
     </row>
@@ -22296,16 +22136,16 @@
       <c r="D17" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E17" s="13">
+      <c r="E17" s="12">
         <v>420</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="4">
         <v>74</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="4">
         <v>59</v>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="4">
         <v>44146.13</v>
       </c>
     </row>
@@ -22313,16 +22153,16 @@
       <c r="D18" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="12">
         <v>731</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="4">
         <v>79</v>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="4">
         <v>31</v>
       </c>
-      <c r="H18" s="12">
+      <c r="H18" s="4">
         <v>43859.520000000004</v>
       </c>
     </row>
@@ -22330,16 +22170,16 @@
       <c r="D19" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E19" s="13">
+      <c r="E19" s="12">
         <v>617</v>
       </c>
-      <c r="F19" s="12">
+      <c r="F19" s="4">
         <v>177</v>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="4">
         <v>28</v>
       </c>
-      <c r="H19" s="12">
+      <c r="H19" s="4">
         <v>42137.53</v>
       </c>
     </row>
@@ -22347,16 +22187,16 @@
       <c r="D20" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="12">
         <v>1151</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="4">
         <v>69</v>
       </c>
-      <c r="G20" s="12">
+      <c r="G20" s="4">
         <v>18</v>
       </c>
-      <c r="H20" s="12">
+      <c r="H20" s="4">
         <v>41544.150000000009</v>
       </c>
     </row>
@@ -22364,16 +22204,16 @@
       <c r="D21" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="12">
         <v>1180</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="4">
         <v>173</v>
       </c>
-      <c r="G21" s="12">
+      <c r="G21" s="4">
         <v>4</v>
       </c>
-      <c r="H21" s="12">
+      <c r="H21" s="4">
         <v>34781.939999999995</v>
       </c>
     </row>
@@ -22381,16 +22221,16 @@
       <c r="D22" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="12">
         <v>924</v>
       </c>
-      <c r="F22" s="12">
+      <c r="F22" s="4">
         <v>218</v>
       </c>
-      <c r="G22" s="12">
+      <c r="G22" s="4">
         <v>30</v>
       </c>
-      <c r="H22" s="12">
+      <c r="H22" s="4">
         <v>29842.950000000004</v>
       </c>
     </row>
@@ -22398,16 +22238,16 @@
       <c r="D23" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="E23" s="13">
+      <c r="E23" s="12">
         <v>246</v>
       </c>
-      <c r="F23" s="12">
+      <c r="F23" s="4">
         <v>172</v>
       </c>
-      <c r="G23" s="12">
+      <c r="G23" s="4">
         <v>17</v>
       </c>
-      <c r="H23" s="12">
+      <c r="H23" s="4">
         <v>18659.18</v>
       </c>
     </row>
@@ -22415,16 +22255,16 @@
       <c r="D24" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E24" s="13">
+      <c r="E24" s="12">
         <v>241</v>
       </c>
-      <c r="F24" s="12">
+      <c r="F24" s="4">
         <v>80</v>
       </c>
-      <c r="G24" s="12">
+      <c r="G24" s="4">
         <v>40</v>
       </c>
-      <c r="H24" s="12">
+      <c r="H24" s="4">
         <v>18368.47</v>
       </c>
     </row>
@@ -22432,16 +22272,16 @@
       <c r="D25" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E25" s="13">
+      <c r="E25" s="12">
         <v>1119</v>
       </c>
-      <c r="F25" s="12">
+      <c r="F25" s="4">
         <v>61</v>
       </c>
-      <c r="G25" s="12">
+      <c r="G25" s="4">
         <v>40</v>
       </c>
-      <c r="H25" s="12">
+      <c r="H25" s="4">
         <v>14672.969999999998</v>
       </c>
     </row>
@@ -22449,16 +22289,16 @@
       <c r="D26" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E26" s="13">
+      <c r="E26" s="12">
         <v>831</v>
       </c>
-      <c r="F26" s="12">
+      <c r="F26" s="4">
         <v>154</v>
       </c>
-      <c r="G26" s="12">
+      <c r="G26" s="4">
         <v>4</v>
       </c>
-      <c r="H26" s="12">
+      <c r="H26" s="4">
         <v>14526.439999999999</v>
       </c>
     </row>
@@ -22466,16 +22306,16 @@
       <c r="D27" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="E27" s="13">
+      <c r="E27" s="12">
         <v>367</v>
       </c>
-      <c r="F27" s="12">
+      <c r="F27" s="4">
         <v>217</v>
       </c>
-      <c r="G27" s="12">
+      <c r="G27" s="4">
         <v>103</v>
       </c>
-      <c r="H27" s="12">
+      <c r="H27" s="4">
         <v>14209.390000000001</v>
       </c>
     </row>
@@ -22483,16 +22323,16 @@
       <c r="D28" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E28" s="13">
+      <c r="E28" s="12">
         <v>977</v>
       </c>
-      <c r="F28" s="12">
+      <c r="F28" s="4">
         <v>166</v>
       </c>
-      <c r="G28" s="12">
+      <c r="G28" s="4">
         <v>55</v>
       </c>
-      <c r="H28" s="12">
+      <c r="H28" s="4">
         <v>12143.710000000001</v>
       </c>
     </row>
@@ -22500,16 +22340,16 @@
       <c r="D29" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E29" s="13">
+      <c r="E29" s="12">
         <v>806</v>
       </c>
-      <c r="F29" s="12">
+      <c r="F29" s="4">
         <v>184</v>
       </c>
-      <c r="G29" s="12">
+      <c r="G29" s="4">
         <v>100</v>
       </c>
-      <c r="H29" s="12">
+      <c r="H29" s="4">
         <v>12040.489999999998</v>
       </c>
     </row>
@@ -22517,16 +22357,16 @@
       <c r="D30" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="12">
         <v>226</v>
       </c>
-      <c r="F30" s="12">
+      <c r="F30" s="4">
         <v>91</v>
       </c>
-      <c r="G30" s="12">
+      <c r="G30" s="4">
         <v>73</v>
       </c>
-      <c r="H30" s="12">
+      <c r="H30" s="4">
         <v>9402.9399999999987</v>
       </c>
     </row>
@@ -22534,16 +22374,16 @@
       <c r="D31" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="12">
         <v>747</v>
       </c>
-      <c r="F31" s="12">
+      <c r="F31" s="4">
         <v>97</v>
       </c>
-      <c r="G31" s="12">
+      <c r="G31" s="4">
         <v>31</v>
       </c>
-      <c r="H31" s="12">
+      <c r="H31" s="4">
         <v>7844.18</v>
       </c>
     </row>
@@ -22551,16 +22391,16 @@
       <c r="D32" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="12">
         <v>848</v>
       </c>
-      <c r="F32" s="12">
+      <c r="F32" s="4">
         <v>99</v>
       </c>
-      <c r="G32" s="12">
+      <c r="G32" s="4">
         <v>84</v>
       </c>
-      <c r="H32" s="12">
+      <c r="H32" s="4">
         <v>6133.4100000000008</v>
       </c>
     </row>
@@ -22568,16 +22408,16 @@
       <c r="D33" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="E33" s="13">
+      <c r="E33" s="12">
         <v>1087</v>
       </c>
-      <c r="F33" s="12">
+      <c r="F33" s="4">
         <v>212</v>
       </c>
-      <c r="G33" s="12">
+      <c r="G33" s="4">
         <v>54</v>
       </c>
-      <c r="H33" s="12">
+      <c r="H33" s="4">
         <v>5002.7100000000009</v>
       </c>
     </row>
@@ -22585,16 +22425,16 @@
       <c r="D34" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E34" s="13">
+      <c r="E34" s="12">
         <v>882</v>
       </c>
-      <c r="F34" s="12">
+      <c r="F34" s="4">
         <v>225</v>
       </c>
-      <c r="G34" s="12">
+      <c r="G34" s="4">
         <v>30</v>
       </c>
-      <c r="H34" s="12">
+      <c r="H34" s="4">
         <v>4278.2</v>
       </c>
     </row>
@@ -22602,16 +22442,16 @@
       <c r="D35" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="E35" s="13">
+      <c r="E35" s="12">
         <v>407</v>
       </c>
-      <c r="F35" s="12">
+      <c r="F35" s="4">
         <v>130</v>
       </c>
-      <c r="G35" s="12">
+      <c r="G35" s="4">
         <v>52</v>
       </c>
-      <c r="H35" s="12">
+      <c r="H35" s="4">
         <v>2829.58</v>
       </c>
     </row>
@@ -22619,16 +22459,16 @@
       <c r="D36" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E36" s="13">
+      <c r="E36" s="12">
         <v>18300</v>
       </c>
-      <c r="F36" s="12">
+      <c r="F36" s="4">
         <v>3619</v>
       </c>
-      <c r="G36" s="12">
+      <c r="G36" s="4">
         <v>1309</v>
       </c>
-      <c r="H36" s="12">
+      <c r="H36" s="4">
         <v>706194.8899999999</v>
       </c>
     </row>
